--- a/data/EEZ_528/EEZ_528.xlsx
+++ b/data/EEZ_528/EEZ_528.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -500,829 +520,860 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1950-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>251</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1950-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>182</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>catch_tonnes</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_tonnes</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_over_npp_percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B13" t="n">
-        <v>172472.391</v>
-      </c>
-      <c r="C13" t="n">
-        <v>76640025.737</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B14" t="n">
-        <v>205663.712</v>
-      </c>
-      <c r="C14" t="n">
-        <v>94632006.89300001</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>catch_tonnes</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_tonnes</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_over_npp_percent</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B15" t="n">
-        <v>185988.997</v>
+        <v>172472.391</v>
       </c>
       <c r="C15" t="n">
-        <v>89468316.51800001</v>
+        <v>76640025.737</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B16" t="n">
-        <v>230187.39</v>
+        <v>205663.712</v>
       </c>
       <c r="C16" t="n">
-        <v>103684349.323</v>
+        <v>94632006.89300001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B17" t="n">
-        <v>215879.918</v>
+        <v>185988.997</v>
       </c>
       <c r="C17" t="n">
-        <v>104738591.674</v>
+        <v>89468316.51800001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B18" t="n">
-        <v>171737.136</v>
+        <v>230187.39</v>
       </c>
       <c r="C18" t="n">
-        <v>90331999.64300001</v>
+        <v>103684349.323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B19" t="n">
-        <v>176220.829</v>
+        <v>215879.918</v>
       </c>
       <c r="C19" t="n">
-        <v>90731802.397</v>
+        <v>104738591.674</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B20" t="n">
-        <v>219327.427</v>
+        <v>171737.136</v>
       </c>
       <c r="C20" t="n">
-        <v>116331930.563</v>
+        <v>90331999.64300001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B21" t="n">
-        <v>207163.79</v>
+        <v>176220.829</v>
       </c>
       <c r="C21" t="n">
-        <v>99073707.40099999</v>
+        <v>90731802.397</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B22" t="n">
-        <v>256767.683</v>
+        <v>219327.427</v>
       </c>
       <c r="C22" t="n">
-        <v>113789089.411</v>
+        <v>116331930.563</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B23" t="n">
-        <v>198335.859</v>
+        <v>207163.79</v>
       </c>
       <c r="C23" t="n">
-        <v>92548587.397</v>
+        <v>99073707.40099999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B24" t="n">
-        <v>217904.649</v>
+        <v>256767.683</v>
       </c>
       <c r="C24" t="n">
-        <v>112120509.866</v>
+        <v>113789089.411</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B25" t="n">
-        <v>215577.526</v>
+        <v>198335.859</v>
       </c>
       <c r="C25" t="n">
-        <v>97366907.678</v>
+        <v>92548587.397</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B26" t="n">
-        <v>253098.308</v>
+        <v>217904.649</v>
       </c>
       <c r="C26" t="n">
-        <v>125232879.566</v>
+        <v>112120509.866</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B27" t="n">
-        <v>289108.571</v>
+        <v>215577.526</v>
       </c>
       <c r="C27" t="n">
-        <v>150530139.884</v>
+        <v>97366907.678</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B28" t="n">
-        <v>245470.398</v>
+        <v>253098.308</v>
       </c>
       <c r="C28" t="n">
-        <v>154541109.349</v>
+        <v>125232879.566</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B29" t="n">
-        <v>281910.736</v>
+        <v>289108.571</v>
       </c>
       <c r="C29" t="n">
-        <v>218667217.401</v>
+        <v>150530139.884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B30" t="n">
-        <v>213161.914</v>
+        <v>245470.398</v>
       </c>
       <c r="C30" t="n">
-        <v>137484842.031</v>
+        <v>154541109.349</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B31" t="n">
-        <v>242601.855</v>
+        <v>281910.736</v>
       </c>
       <c r="C31" t="n">
-        <v>176430240.495</v>
+        <v>218667217.401</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B32" t="n">
-        <v>317352.501</v>
+        <v>213161.914</v>
       </c>
       <c r="C32" t="n">
-        <v>260799425.529</v>
+        <v>137484842.031</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B33" t="n">
-        <v>385998.451</v>
+        <v>242601.855</v>
       </c>
       <c r="C33" t="n">
-        <v>357138437.586</v>
+        <v>176430240.495</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B34" t="n">
-        <v>297050.748</v>
+        <v>317352.501</v>
       </c>
       <c r="C34" t="n">
-        <v>241839166.411</v>
+        <v>260799425.529</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B35" t="n">
-        <v>256550.714</v>
+        <v>385998.451</v>
       </c>
       <c r="C35" t="n">
-        <v>205773097.681</v>
+        <v>357138437.586</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B36" t="n">
-        <v>266333.879</v>
+        <v>297050.748</v>
       </c>
       <c r="C36" t="n">
-        <v>195823828.698</v>
+        <v>241839166.411</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B37" t="n">
-        <v>262729.849</v>
+        <v>256550.714</v>
       </c>
       <c r="C37" t="n">
-        <v>184654430.814</v>
+        <v>205773097.681</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B38" t="n">
-        <v>273487.086</v>
+        <v>266333.879</v>
       </c>
       <c r="C38" t="n">
-        <v>156739101.492</v>
+        <v>195823828.698</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B39" t="n">
-        <v>271096.248</v>
+        <v>262729.849</v>
       </c>
       <c r="C39" t="n">
-        <v>158000407.899</v>
+        <v>184654430.814</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B40" t="n">
-        <v>217743.215</v>
+        <v>273487.086</v>
       </c>
       <c r="C40" t="n">
-        <v>117604201.11</v>
+        <v>156739101.492</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B41" t="n">
-        <v>222856.185</v>
+        <v>271096.248</v>
       </c>
       <c r="C41" t="n">
-        <v>128472020.854</v>
+        <v>158000407.899</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B42" t="n">
-        <v>228120.399</v>
+        <v>217743.215</v>
       </c>
       <c r="C42" t="n">
-        <v>144127653.224</v>
+        <v>117604201.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B43" t="n">
-        <v>245807.294</v>
+        <v>222856.185</v>
       </c>
       <c r="C43" t="n">
-        <v>135925619.281</v>
+        <v>128472020.854</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B44" t="n">
-        <v>240911.827</v>
+        <v>228120.399</v>
       </c>
       <c r="C44" t="n">
-        <v>139013560.73</v>
+        <v>144127653.224</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B45" t="n">
-        <v>262183.065</v>
+        <v>245807.294</v>
       </c>
       <c r="C45" t="n">
-        <v>135633442.184</v>
+        <v>135925619.281</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B46" t="n">
-        <v>236724.39</v>
+        <v>240911.827</v>
       </c>
       <c r="C46" t="n">
-        <v>120611947.332</v>
+        <v>139013560.73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B47" t="n">
-        <v>250021.704</v>
+        <v>262183.065</v>
       </c>
       <c r="C47" t="n">
-        <v>111723363.361</v>
+        <v>135633442.184</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B48" t="n">
-        <v>288842.103</v>
+        <v>236724.39</v>
       </c>
       <c r="C48" t="n">
-        <v>121359416.099</v>
+        <v>120611947.332</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B49" t="n">
-        <v>298978.92</v>
+        <v>250021.704</v>
       </c>
       <c r="C49" t="n">
-        <v>121387673.314</v>
+        <v>111723363.361</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B50" t="n">
-        <v>264256.313</v>
+        <v>288842.103</v>
       </c>
       <c r="C50" t="n">
-        <v>107451921.395</v>
+        <v>121359416.099</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B51" t="n">
-        <v>302951.053</v>
+        <v>298978.92</v>
       </c>
       <c r="C51" t="n">
-        <v>115031771.047</v>
+        <v>121387673.314</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B52" t="n">
-        <v>323918.128</v>
+        <v>264256.313</v>
       </c>
       <c r="C52" t="n">
-        <v>98351139.324</v>
+        <v>107451921.395</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B53" t="n">
-        <v>264054.202</v>
+        <v>302951.053</v>
       </c>
       <c r="C53" t="n">
-        <v>83256242.398</v>
+        <v>115031771.047</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B54" t="n">
-        <v>271756.197</v>
+        <v>323918.128</v>
       </c>
       <c r="C54" t="n">
-        <v>84872333.792</v>
+        <v>98351139.324</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B55" t="n">
-        <v>293880.05</v>
+        <v>264054.202</v>
       </c>
       <c r="C55" t="n">
-        <v>85313454.969</v>
+        <v>83256242.398</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B56" t="n">
-        <v>243787.003</v>
+        <v>271756.197</v>
       </c>
       <c r="C56" t="n">
-        <v>79503200.061</v>
+        <v>84872333.792</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B57" t="n">
-        <v>270596.736</v>
+        <v>293880.05</v>
       </c>
       <c r="C57" t="n">
-        <v>77996576.55400001</v>
+        <v>85313454.969</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B58" t="n">
-        <v>291701.009</v>
+        <v>243787.003</v>
       </c>
       <c r="C58" t="n">
-        <v>87457464.427</v>
+        <v>79503200.061</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B59" t="n">
-        <v>211821.492</v>
+        <v>270596.736</v>
       </c>
       <c r="C59" t="n">
-        <v>69239974.552</v>
+        <v>77996576.55400001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B60" t="n">
-        <v>239136.473</v>
+        <v>291701.009</v>
       </c>
       <c r="C60" t="n">
-        <v>72500818.873</v>
+        <v>87457464.427</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B61" t="n">
-        <v>256529.462</v>
+        <v>211821.492</v>
       </c>
       <c r="C61" t="n">
-        <v>71145486.036</v>
+        <v>69239974.552</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B62" t="n">
-        <v>234060.505</v>
+        <v>239136.473</v>
       </c>
       <c r="C62" t="n">
-        <v>65413621.414</v>
+        <v>72500818.873</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B63" t="n">
-        <v>236276.907</v>
+        <v>256529.462</v>
       </c>
       <c r="C63" t="n">
-        <v>63910909.003</v>
+        <v>71145486.036</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B64" t="n">
-        <v>238117.239</v>
+        <v>234060.505</v>
       </c>
       <c r="C64" t="n">
-        <v>66260551.963</v>
+        <v>65413621.414</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B65" t="n">
-        <v>227223.5</v>
+        <v>236276.907</v>
       </c>
       <c r="C65" t="n">
-        <v>63543735.714</v>
+        <v>63910909.003</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B66" t="n">
-        <v>179864.053</v>
+        <v>238117.239</v>
       </c>
       <c r="C66" t="n">
-        <v>52356758.733</v>
+        <v>66260551.963</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B67" t="n">
-        <v>178635.716</v>
+        <v>227223.5</v>
       </c>
       <c r="C67" t="n">
-        <v>49062959.68</v>
+        <v>63543735.714</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B68" t="n">
-        <v>138835.334</v>
+        <v>179864.053</v>
       </c>
       <c r="C68" t="n">
-        <v>39771215.254</v>
+        <v>52356758.733</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B69" t="n">
-        <v>152503.057</v>
+        <v>178635.716</v>
       </c>
       <c r="C69" t="n">
-        <v>42692631.16</v>
+        <v>49062959.68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B70" t="n">
-        <v>116124.736</v>
+        <v>138835.334</v>
       </c>
       <c r="C70" t="n">
-        <v>34850375.485</v>
+        <v>39771215.254</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B71" t="n">
-        <v>123348.268</v>
+        <v>152503.057</v>
       </c>
       <c r="C71" t="n">
-        <v>37255003.316</v>
+        <v>42692631.16</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B72" t="n">
-        <v>153439.308</v>
+        <v>116124.736</v>
       </c>
       <c r="C72" t="n">
-        <v>45796564.613</v>
+        <v>34850375.485</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B73" t="n">
-        <v>168904.222</v>
+        <v>123348.268</v>
       </c>
       <c r="C73" t="n">
-        <v>46155299.959</v>
+        <v>37255003.316</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B74" t="n">
-        <v>162841.408</v>
+        <v>153439.308</v>
       </c>
       <c r="C74" t="n">
-        <v>44248788.709</v>
+        <v>45796564.613</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B75" t="n">
-        <v>102611.391</v>
+        <v>168904.222</v>
       </c>
       <c r="C75" t="n">
-        <v>34510567.077</v>
+        <v>46155299.959</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B76" t="n">
-        <v>141241.269</v>
+        <v>162841.408</v>
       </c>
       <c r="C76" t="n">
-        <v>41719092.851</v>
+        <v>44248788.709</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B77" t="n">
-        <v>129072.142</v>
+        <v>102611.391</v>
       </c>
       <c r="C77" t="n">
-        <v>40464875.059</v>
+        <v>34510567.077</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B78" t="n">
-        <v>157936.584</v>
+        <v>141241.269</v>
       </c>
       <c r="C78" t="n">
-        <v>40964928.939</v>
+        <v>41719092.851</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B79" t="n">
-        <v>123243.941</v>
+        <v>129072.142</v>
       </c>
       <c r="C79" t="n">
-        <v>37426162.842</v>
+        <v>40464875.059</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B80" t="n">
-        <v>153530.437</v>
+        <v>157936.584</v>
       </c>
       <c r="C80" t="n">
-        <v>43475664.498</v>
+        <v>40964928.939</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B81" t="n">
-        <v>131745.285</v>
+        <v>123243.941</v>
       </c>
       <c r="C81" t="n">
-        <v>40514616.385</v>
+        <v>37426162.842</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B82" t="n">
-        <v>101104.757</v>
+        <v>153530.437</v>
       </c>
       <c r="C82" t="n">
-        <v>32412118.312</v>
+        <v>43475664.498</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B83" t="n">
+        <v>131745.285</v>
+      </c>
+      <c r="C83" t="n">
+        <v>40514616.385</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101104.757</v>
+      </c>
+      <c r="C84" t="n">
+        <v>32412118.312</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
         </is>
@@ -1439,355 +1490,215 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AY1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AZ1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="BA1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="BB1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BC1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BD1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BE1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BF1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BG1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BH1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BI1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BJ1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BK1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BL1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BM1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BN1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BO1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BP1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BQ1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BR1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BS1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BT1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BU1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BV1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1951</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1952</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1957</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1959</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1960</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1962</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1964</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1965</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1966</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1967</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1968</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1972</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AZ1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="BA1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="BB1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BC1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BD1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BE1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BF1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BG1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BH1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BI1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BJ1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BK1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BL1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BM1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BN1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BO1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BP1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BQ1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BR1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BS1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BT1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BU1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BV1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -62460,6 +62371,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62638,355 +62788,215 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BI4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BJ4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BK4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BL4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BM4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BN4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BO4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BP4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BQ4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BR4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BS4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BT4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1955</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1957</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1959</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1963</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1964</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1965</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1966</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1967</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -103034,7 +103044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
